--- a/backend/data/financials_by_company/002208.SZ.xlsx
+++ b/backend/data/financials_by_company/002208.SZ.xlsx
@@ -3858,152 +3858,152 @@
       </c>
       <c r="DB1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
         <is>
           <t>longName</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>exchange</t>
         </is>
       </c>
       <c r="EF1" t="inlineStr">
@@ -4045,12 +4045,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Building A</t>
+          <t>Amber Five Rings City International</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Amber Fifth Ring City Intern Floor 10-14 No. 100 Qianshan Road,Shushan District</t>
+          <t>Floors 9-14, Block A No. 100 Qianshan Road Shushan District</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Hefei Urban Construction Development Co., Ltd engages in the real estate development business under the Amber brand name in China. The company develops and constructs residential, commercial, and industrial real estate properties; and office buildings. It is also engaged in property management and leasing activities, as well as offers construction project management consulting services. Hefei Urban Construction Development Co., Ltd was founded in 1999 and is headquartered in Hefei, China.</t>
+          <t>Hefei Urban Construction Development Co., Ltd engages in the real estate development business under the Amber brand name in China. The company develops and constructs residential, commercial, and industrial real estate properties; and office buildings. It is also involved in property management, urban renewal, and leasing activities. In addition, the company offers construction management consulting services. Hefei Urban Construction Development Co., Ltd was founded in 1999 and is headquartered in Hefei, China.</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -4138,28 +4138,28 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>18.77</v>
+        <v>19.06</v>
       </c>
       <c r="V2" t="n">
-        <v>17.31</v>
+        <v>15.73</v>
       </c>
       <c r="W2" t="n">
-        <v>17.99</v>
+        <v>18.22</v>
       </c>
       <c r="X2" t="n">
-        <v>19.63</v>
+        <v>19.98</v>
       </c>
       <c r="Y2" t="n">
-        <v>18.77</v>
+        <v>19.06</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.31</v>
+        <v>15.73</v>
       </c>
       <c r="AA2" t="n">
-        <v>17.99</v>
+        <v>18.22</v>
       </c>
       <c r="AB2" t="n">
-        <v>19.63</v>
+        <v>19.98</v>
       </c>
       <c r="AC2" t="n">
         <v>1721088000</v>
@@ -4171,28 +4171,28 @@
         <v>1.09</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.369</v>
+        <v>1.345</v>
       </c>
       <c r="AG2" t="n">
-        <v>109287920</v>
+        <v>91510390</v>
       </c>
       <c r="AH2" t="n">
-        <v>109287920</v>
+        <v>91510390</v>
       </c>
       <c r="AI2" t="n">
-        <v>61501455</v>
+        <v>72262449</v>
       </c>
       <c r="AJ2" t="n">
-        <v>71947099</v>
+        <v>104572616</v>
       </c>
       <c r="AK2" t="n">
-        <v>71947099</v>
+        <v>104572616</v>
       </c>
       <c r="AL2" t="n">
-        <v>18.18</v>
+        <v>19.22</v>
       </c>
       <c r="AM2" t="n">
-        <v>18.19</v>
+        <v>19.24</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -4201,10 +4201,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>14603846656</v>
+        <v>15439269888</v>
       </c>
       <c r="AQ2" t="n">
-        <v>15077788850</v>
+        <v>16226496258</v>
       </c>
       <c r="AR2" t="n">
         <v>6.38</v>
@@ -4219,13 +4219,13 @@
         <v>1.734615</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.3502523</v>
+        <v>1.4274944</v>
       </c>
       <c r="AW2" t="n">
-        <v>16.1154</v>
+        <v>17.1126</v>
       </c>
       <c r="AX2" t="n">
-        <v>13.28625</v>
+        <v>13.78895</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>27685713920</v>
+        <v>28521138176</v>
       </c>
       <c r="BD2" t="n">
         <v>-0.05129</v>
@@ -4254,10 +4254,10 @@
         <v>803291894</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.6150999700000001</v>
+        <v>0.60632</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.00932</v>
+        <v>0.009339999999999999</v>
       </c>
       <c r="BI2" t="n">
         <v>803291894</v>
@@ -4266,7 +4266,7 @@
         <v>7.373</v>
       </c>
       <c r="BK2" t="n">
-        <v>2.4657533</v>
+        <v>2.6068084</v>
       </c>
       <c r="BL2" t="n">
         <v>1767139200</v>
@@ -4292,16 +4292,16 @@
         <v>1557792000</v>
       </c>
       <c r="BS2" t="n">
-        <v>2.56</v>
+        <v>2.637</v>
       </c>
       <c r="BT2" t="n">
-        <v>61.133</v>
+        <v>62.978</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.7242379</v>
+        <v>1.8575711</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="BW2" t="n">
         <v>0.08500000000000001</v>
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="BZ2" t="n">
-        <v>18.18</v>
+        <v>19.22</v>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
@@ -4414,110 +4414,110 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DB2" t="n">
-        <v>-3.1433146</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>18.18</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>-0.5900001499999999</v>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>17.99 - 19.63</t>
-        </is>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>HEFEI URBAN CONSTRUCTION DEVELO</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DE2" t="n">
+        <v>1783062243</v>
       </c>
       <c r="DF2" t="inlineStr">
         <is>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="DG2" t="n">
+        <v>0.8394536</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>1201483800000</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>0.15999985</v>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>18.22 - 19.98</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
           <t>Shenzhen</t>
         </is>
       </c>
-      <c r="DG2" t="n">
-        <v>61501455</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>1.8495297</v>
-      </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DM2" t="n">
+        <v>72262449</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>12.839999</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>2.012539</v>
+      </c>
+      <c r="DP2" t="inlineStr">
         <is>
           <t>6.38 - 26.36</t>
         </is>
       </c>
-      <c r="DK2" t="n">
-        <v>-8.18</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>-0.31031868</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>172.4238</v>
-      </c>
-      <c r="DN2" t="n">
+      <c r="DQ2" t="n">
+        <v>-7.1400013</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.270865</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>185.75711</v>
+      </c>
+      <c r="DT2" t="n">
         <v>1619521140</v>
       </c>
-      <c r="DO2" t="n">
+      <c r="DU2" t="n">
         <v>1619521140</v>
       </c>
-      <c r="DP2" t="n">
+      <c r="DV2" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="DQ2" t="n">
-        <v>2.0646</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0.12811348</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>4.89375</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0.36833194</v>
-      </c>
-      <c r="DU2" t="n">
+      <c r="DW2" t="n">
+        <v>2.107399</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>0.12314896</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>5.4310493</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>0.39386967</v>
+      </c>
+      <c r="EA2" t="n">
         <v>15</v>
       </c>
-      <c r="DV2" t="n">
+      <c r="EB2" t="n">
         <v>15</v>
       </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>HEFEI URBAN CONSTRUCTION DEVELO</t>
-        </is>
-      </c>
-      <c r="DX2" t="inlineStr">
+      <c r="EC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="ED2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EE2" t="inlineStr">
         <is>
           <t>Hefei Urban Construction Development Co., Ltd</t>
-        </is>
-      </c>
-      <c r="DY2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EA2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>1201483800000</v>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="ED2" t="n">
-        <v>1782111894</v>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>SHZ</t>
         </is>
       </c>
       <c r="EF2" t="inlineStr">
